--- a/backend/wp_templates/G/G14 信用减值损失.xlsx
+++ b/backend/wp_templates/G/G14 信用减值损失.xlsx
@@ -10200,7 +10200,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="195">
-        <f>G11+H11</f>
+        <f>G11-H11</f>
         <v>0</v>
       </c>
       <c r="L11" s="120" t="b">
@@ -10231,7 +10231,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="195">
-        <f t="shared" ref="K12:K19" si="2">G12+H12</f>
+        <f t="shared" ref="K12:K19" si="2">G12-H12</f>
         <v>0</v>
       </c>
       <c r="L12" s="120" t="b">
